--- a/out/ginot_hair_plans.xlsx
+++ b/out/ginot_hair_plans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="plans" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="plans" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="counts" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11915,7 +11915,7 @@
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
+          <t>2020-07-13</t>
         </is>
       </c>
       <c r="N125" t="n">
@@ -21024,7 +21024,7 @@
       <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="N226" t="n">
@@ -21936,7 +21936,7 @@
       <c r="L237" t="inlineStr"/>
       <c r="M237" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="N237" t="n">
@@ -22024,7 +22024,7 @@
       <c r="L238" t="inlineStr"/>
       <c r="M238" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="N238" t="n">
@@ -22903,7 +22903,7 @@
       <c r="L248" t="inlineStr"/>
       <c r="M248" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="N248" t="n">
@@ -23740,7 +23740,11 @@
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
       <c r="N258" t="n">
         <v>1.455</v>
       </c>
@@ -24567,7 +24571,11 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr"/>
-      <c r="M268" t="inlineStr"/>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="N268" t="n">
         <v>7.311</v>
       </c>
@@ -25386,7 +25394,7 @@
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="N278" t="n">
@@ -26112,7 +26120,7 @@
       <c r="L287" t="inlineStr"/>
       <c r="M287" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="N287" t="n">
@@ -27332,7 +27340,11 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr"/>
       <c r="L302" t="inlineStr"/>
-      <c r="M302" t="inlineStr"/>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
       <c r="N302" t="n">
         <v>8.739000000000001</v>
       </c>
@@ -27418,7 +27430,7 @@
       <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N303" t="n">
@@ -27555,7 +27567,11 @@
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr"/>
-      <c r="M305" t="inlineStr"/>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="N305" t="n">
         <v>7.324</v>
       </c>
@@ -28010,7 +28026,11 @@
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr"/>
       <c r="L311" t="inlineStr"/>
-      <c r="M311" t="inlineStr"/>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
       <c r="N311" t="n">
         <v>7.366</v>
       </c>

--- a/out/ginot_hair_plans.xlsx
+++ b/out/ginot_hair_plans.xlsx
@@ -22680,7 +22680,7 @@
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="T260" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>

--- a/out/ginot_hair_plans.xlsx
+++ b/out/ginot_hair_plans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="plans" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="counts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="plans" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counts" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/out/ginot_hair_plans.xlsx
+++ b/out/ginot_hair_plans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="plans" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="plans" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="counts" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/out/ginot_hair_plans.xlsx
+++ b/out/ginot_hair_plans.xlsx
@@ -22606,7 +22606,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>פרסום אישור</t>
+          <t>התכנית אושרה</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -24547,12 +24547,12 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>הפקדה להתנגדויות/השגות</t>
+          <t>אישור</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>פרסום הפקדה</t>
+          <t>פרסום אישור</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -24597,7 +24597,7 @@
       </c>
       <c r="T268" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="T295" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -31021,7 +31021,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3">
@@ -31051,7 +31051,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">

--- a/out/ginot_hair_plans.xlsx
+++ b/out/ginot_hair_plans.xlsx
@@ -25394,7 +25394,7 @@
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="N278" t="n">

--- a/out/ginot_hair_plans.xlsx
+++ b/out/ginot_hair_plans.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T352"/>
+  <dimension ref="A1:T353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17996,11 +17996,7 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>2023-12-29</t>
-        </is>
-      </c>
+      <c r="M192" t="inlineStr"/>
       <c r="N192" t="n">
         <v>13.337</v>
       </c>
@@ -18027,7 +18023,7 @@
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -21987,7 +21983,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>פרסום הפקדה</t>
+          <t>בתהליך הפקדה</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -22976,11 +22972,7 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+      <c r="M249" t="inlineStr"/>
       <c r="N249" t="n">
         <v>4.478</v>
       </c>
@@ -23916,11 +23908,7 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>2025-07-17</t>
-        </is>
-      </c>
+      <c r="M260" t="inlineStr"/>
       <c r="N260" t="n">
         <v>4.251</v>
       </c>
@@ -24905,11 +24893,7 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>2026-12-12</t>
-        </is>
-      </c>
+      <c r="M272" t="inlineStr"/>
       <c r="N272" t="n">
         <v>3.86</v>
       </c>
@@ -24985,11 +24969,7 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
+      <c r="M273" t="inlineStr"/>
       <c r="N273" t="n">
         <v>2.449</v>
       </c>
@@ -25560,11 +25540,7 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
+      <c r="M280" t="inlineStr"/>
       <c r="N280" t="n">
         <v>6622</v>
       </c>
@@ -25640,11 +25616,7 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
+      <c r="M281" t="inlineStr"/>
       <c r="N281" t="n">
         <v>4.895</v>
       </c>
@@ -25846,7 +25818,7 @@
       </c>
       <c r="T283" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -25895,11 +25867,7 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr"/>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
+      <c r="M284" t="inlineStr"/>
       <c r="N284" t="n">
         <v>9.829000000000001</v>
       </c>
@@ -26038,11 +26006,7 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr"/>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>2026-12-12</t>
-        </is>
-      </c>
+      <c r="M286" t="inlineStr"/>
       <c r="N286" t="n">
         <v>4.405</v>
       </c>
@@ -26198,11 +26162,7 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr"/>
-      <c r="M288" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
+      <c r="M288" t="inlineStr"/>
       <c r="N288" t="n">
         <v>0.787</v>
       </c>
@@ -26422,11 +26382,7 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr"/>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
+      <c r="M291" t="inlineStr"/>
       <c r="N291" t="n">
         <v>3.584</v>
       </c>
@@ -26502,11 +26458,7 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr"/>
-      <c r="M292" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
+      <c r="M292" t="inlineStr"/>
       <c r="N292" t="n">
         <v>0.649</v>
       </c>
@@ -26770,11 +26722,7 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr"/>
       <c r="L295" t="inlineStr"/>
-      <c r="M295" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
+      <c r="M295" t="inlineStr"/>
       <c r="N295" t="n">
         <v>3.175</v>
       </c>
@@ -26850,11 +26798,7 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr"/>
-      <c r="M296" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
+      <c r="M296" t="inlineStr"/>
       <c r="N296" t="n">
         <v>1.063</v>
       </c>
@@ -27056,12 +27000,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>בבדיקה תכנונית</t>
+          <t>במילוי תנאים להפקדה</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>קיום תנאי סף</t>
+          <t>החלטה בדיון</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -27080,7 +27024,11 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="I299" t="inlineStr"/>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr"/>
@@ -27111,7 +27059,7 @@
       </c>
       <c r="T299" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -27647,11 +27595,7 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr"/>
       <c r="L306" t="inlineStr"/>
-      <c r="M306" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
+      <c r="M306" t="inlineStr"/>
       <c r="N306" t="n">
         <v>5.2134</v>
       </c>
@@ -27727,11 +27671,7 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr"/>
       <c r="L307" t="inlineStr"/>
-      <c r="M307" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
+      <c r="M307" t="inlineStr"/>
       <c r="N307" t="n">
         <v>1.969</v>
       </c>
@@ -27807,11 +27747,7 @@
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr"/>
       <c r="L308" t="inlineStr"/>
-      <c r="M308" t="inlineStr">
-        <is>
-          <t>2026-12-12</t>
-        </is>
-      </c>
+      <c r="M308" t="inlineStr"/>
       <c r="N308" t="n">
         <v>4.12</v>
       </c>
@@ -27882,11 +27818,7 @@
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr"/>
       <c r="L309" t="inlineStr"/>
-      <c r="M309" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
+      <c r="M309" t="inlineStr"/>
       <c r="N309" t="n">
         <v>2.079</v>
       </c>
@@ -28322,11 +28254,7 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr"/>
-      <c r="M315" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
+      <c r="M315" t="inlineStr"/>
       <c r="N315" t="n">
         <v>13622</v>
       </c>
@@ -28795,7 +28723,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>פרסום אישור</t>
+          <t>התכנית אושרה</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -28833,7 +28761,11 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="L322" t="inlineStr"/>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M322" t="inlineStr">
         <is>
           <t>2026-10-06</t>
@@ -28865,7 +28797,7 @@
       </c>
       <c r="T322" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -29190,11 +29122,7 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr"/>
-      <c r="M327" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
+      <c r="M327" t="inlineStr"/>
       <c r="N327" t="n">
         <v>3.69</v>
       </c>
@@ -29888,17 +29816,17 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>שינוי קווי בנין עבור בינוי ברח' מבוא יורם 1 , ירושלים.</t>
+          <t>שינוי קווי בניין לשם שינוי תכנון ללא תוספת שטחים-מבוא יורם 1</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>בבדיקה תכנונית</t>
+          <t>הפקדה להתנגדויות/השגות</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>קיום תנאי סף</t>
+          <t>פרסום הפקדה</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -29944,7 +29872,7 @@
       </c>
       <c r="T337" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -30637,22 +30565,17 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>101-0110510</t>
+          <t>101-1566306</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>מתחם פינוי ובינוי אלכסנדריון, גוננים - ירושלים</t>
+          <t>רחוב חלפתא 3 בירושלים הרחבת דיור לדירה קיימת</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>אישור</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>התכנית אושרה</t>
+          <t>בבדיקה תכנונית</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -30660,35 +30583,23 @@
           <t>תכנית מתאר מקומית</t>
         </is>
       </c>
-      <c r="F348" t="inlineStr"/>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>2014-10-23</t>
-        </is>
-      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr"/>
       <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr"/>
-      <c r="J348" t="inlineStr">
-        <is>
-          <t>2014-08-12</t>
-        </is>
-      </c>
+      <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr"/>
-      <c r="L348" t="inlineStr">
-        <is>
-          <t>2015-06-28</t>
-        </is>
-      </c>
-      <c r="M348" t="inlineStr">
-        <is>
-          <t>2014-10-11</t>
-        </is>
-      </c>
+      <c r="L348" t="inlineStr"/>
+      <c r="M348" t="inlineStr"/>
       <c r="N348" t="n">
-        <v>18.687</v>
+        <v>1607</v>
       </c>
       <c r="O348" t="n">
-        <v>19.4</v>
+        <v>1.6</v>
       </c>
       <c r="P348" t="inlineStr">
         <is>
@@ -30697,11 +30608,11 @@
       </c>
       <c r="Q348" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1000248067/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005522198/310</t>
         </is>
       </c>
       <c r="R348" t="n">
-        <v>1000248067</v>
+        <v>1005522198</v>
       </c>
       <c r="S348" t="inlineStr">
         <is>
@@ -30710,61 +30621,65 @@
       </c>
       <c r="T348" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>101-1158146</t>
+          <t>101-0110510</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>בית הנוער העברי</t>
+          <t>מתחם פינוי ובינוי אלכסנדריון, גוננים - ירושלים</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>במילוי תנאים להפקדה</t>
+          <t>אישור</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>החלטה בדיון</t>
+          <t>התכנית אושרה</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>תכנית מפורטת</t>
+          <t>תכנית מתאר מקומית</t>
         </is>
       </c>
       <c r="F349" t="inlineStr"/>
-      <c r="G349" t="inlineStr"/>
-      <c r="H349" t="inlineStr">
-        <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="I349" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="J349" t="inlineStr"/>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>2014-10-23</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr"/>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>2014-08-12</t>
+        </is>
+      </c>
       <c r="K349" t="inlineStr"/>
-      <c r="L349" t="inlineStr"/>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>2015-06-28</t>
+        </is>
+      </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2014-10-11</t>
         </is>
       </c>
       <c r="N349" t="n">
-        <v>26.859</v>
+        <v>18.687</v>
       </c>
       <c r="O349" t="n">
-        <v>26.9</v>
+        <v>19.4</v>
       </c>
       <c r="P349" t="inlineStr">
         <is>
@@ -30773,11 +30688,11 @@
       </c>
       <c r="Q349" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005267674/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1000248067/310</t>
         </is>
       </c>
       <c r="R349" t="n">
-        <v>1005267674</v>
+        <v>1000248067</v>
       </c>
       <c r="S349" t="inlineStr">
         <is>
@@ -30786,19 +30701,19 @@
       </c>
       <c r="T349" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2025-07-27</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>101-1236579</t>
+          <t>101-1158146</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>מתחם גוננים</t>
+          <t>בית הנוער העברי</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -30813,34 +30728,30 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>תכנית מתאר מקומית</t>
+          <t>תכנית מפורטת</t>
         </is>
       </c>
       <c r="F350" t="inlineStr"/>
       <c r="G350" t="inlineStr"/>
       <c r="H350" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr"/>
-      <c r="M350" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
+      <c r="M350" t="inlineStr"/>
       <c r="N350" t="n">
-        <v>58.047</v>
+        <v>26.859</v>
       </c>
       <c r="O350" t="n">
-        <v>58.1</v>
+        <v>26.9</v>
       </c>
       <c r="P350" t="inlineStr">
         <is>
@@ -30849,11 +30760,11 @@
       </c>
       <c r="Q350" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005317984/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005267674/310</t>
         </is>
       </c>
       <c r="R350" t="n">
-        <v>1005317984</v>
+        <v>1005267674</v>
       </c>
       <c r="S350" t="inlineStr">
         <is>
@@ -30862,73 +30773,86 @@
       </c>
       <c r="T350" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>תתל/ 108/ 77-78</t>
+          <t>101-1236579</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>מסילת רכבת בירושלים</t>
+          <t>מתחם גוננים</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>אישור</t>
+          <t>במילוי תנאים להפקדה</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>התכנית אושרה</t>
+          <t>החלטה בדיון</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>הודעה לפי סעיף 77 ו 78 לחוק התכנון והבניה</t>
+          <t>תכנית מתאר מקומית</t>
         </is>
       </c>
       <c r="F351" t="inlineStr"/>
       <c r="G351" t="inlineStr"/>
-      <c r="H351" t="inlineStr"/>
-      <c r="I351" t="inlineStr"/>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr"/>
       <c r="M351" t="inlineStr"/>
       <c r="N351" t="n">
-        <v>1000.664</v>
+        <v>58.047</v>
       </c>
       <c r="O351" t="n">
-        <v>83.09999999999999</v>
+        <v>58.1</v>
       </c>
       <c r="P351" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="Q351" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/99001010241/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005317984/310</t>
         </is>
       </c>
       <c r="R351" t="n">
-        <v>99001010241</v>
+        <v>1005317984</v>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
       </c>
       <c r="T351" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>תתל/ 108/ סעיף-78-77</t>
+          <t>תתל/ 108/ 77-78</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -30948,7 +30872,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>הודעה לפי ס' 76 ג1 ו-77 וקביעת תנאים לפי ס' 78</t>
+          <t>הודעה לפי סעיף 77 ו 78 לחוק התכנון והבניה</t>
         </is>
       </c>
       <c r="F352" t="inlineStr"/>
@@ -30957,32 +30881,91 @@
       <c r="I352" t="inlineStr"/>
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr"/>
-      <c r="L352" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
+      <c r="L352" t="inlineStr"/>
       <c r="M352" t="inlineStr"/>
       <c r="N352" t="n">
+        <v>1000.664</v>
+      </c>
+      <c r="O352" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>https://mavat.iplan.gov.il/SV4/1/99001010241/310</t>
+        </is>
+      </c>
+      <c r="R352" t="n">
+        <v>99001010241</v>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>תתל/ 108/ סעיף-78-77</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>מסילת רכבת בירושלים</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>אישור</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>התכנית אושרה</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>הודעה לפי ס' 76 ג1 ו-77 וקביעת תנאים לפי ס' 78</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr"/>
+      <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr"/>
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="n">
         <v>777.669</v>
       </c>
-      <c r="O352" t="n">
+      <c r="O353" t="n">
         <v>80.3</v>
       </c>
-      <c r="P352" t="inlineStr">
+      <c r="P353" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
       </c>
-      <c r="Q352" t="inlineStr">
+      <c r="Q353" t="inlineStr">
         <is>
           <t>https://mavat.iplan.gov.il/SV4/1/99005229984/310</t>
         </is>
       </c>
-      <c r="R352" t="n">
+      <c r="R353" t="n">
         <v>99005229984</v>
       </c>
-      <c r="T352" t="inlineStr">
+      <c r="T353" t="inlineStr">
         <is>
           <t>2022-10-26</t>
         </is>
@@ -31031,7 +31014,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -31041,7 +31024,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -31051,7 +31034,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -31093,7 +31076,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">

--- a/out/ginot_hair_plans.xlsx
+++ b/out/ginot_hair_plans.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T353"/>
+  <dimension ref="A1:T355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17996,7 +17996,11 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2026-12-24</t>
+        </is>
+      </c>
       <c r="N192" t="n">
         <v>13.337</v>
       </c>
@@ -22840,7 +22844,7 @@
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -23112,7 +23116,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>הפקדה להתנגדויות/השגות</t>
+          <t>הכרעה בהתנגדויות / אישור</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -23935,7 +23939,7 @@
       </c>
       <c r="T260" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -24559,11 +24563,7 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr"/>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
+      <c r="M268" t="inlineStr"/>
       <c r="N268" t="n">
         <v>7.311</v>
       </c>
@@ -28872,12 +28872,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>101-1449511</t>
+          <t>101-1514884</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>התחדשות עירונית ברחוב ברוריה 1, בן גמלא 16 ו-18.</t>
+          <t>מתחם מגורים רח' ברל לוקר, ירושלים</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -28887,7 +28887,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>קיום תנאי סף</t>
+          <t>קבלת תכנית</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -28897,13 +28897,13 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
@@ -28912,10 +28912,10 @@
       <c r="L324" t="inlineStr"/>
       <c r="M324" t="inlineStr"/>
       <c r="N324" t="n">
-        <v>3.89</v>
+        <v>6.415</v>
       </c>
       <c r="O324" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="P324" t="inlineStr">
         <is>
@@ -28924,11 +28924,11 @@
       </c>
       <c r="Q324" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005450690/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005490802/310</t>
         </is>
       </c>
       <c r="R324" t="n">
-        <v>1005450690</v>
+        <v>1005490802</v>
       </c>
       <c r="S324" t="inlineStr">
         <is>
@@ -28937,19 +28937,19 @@
       </c>
       <c r="T324" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>101-1335496</t>
+          <t>101-1449511</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>הפיכת שטח שרות לעיקרי רח' עמק רפאים 13, ירושלים</t>
+          <t>התחדשות עירונית ברחוב ברוריה 1, בן גמלא 16 ו-18.</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -28969,21 +28969,25 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G325" t="inlineStr"/>
-      <c r="H325" t="inlineStr"/>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
       <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr"/>
       <c r="M325" t="inlineStr"/>
       <c r="N325" t="n">
-        <v>1.194</v>
+        <v>3.89</v>
       </c>
       <c r="O325" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="P325" t="inlineStr">
         <is>
@@ -28992,11 +28996,11 @@
       </c>
       <c r="Q325" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005380806/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005450690/310</t>
         </is>
       </c>
       <c r="R325" t="n">
-        <v>1005380806</v>
+        <v>1005450690</v>
       </c>
       <c r="S325" t="inlineStr">
         <is>
@@ -29005,19 +29009,19 @@
       </c>
       <c r="T325" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>101-1523851</t>
+          <t>101-1335496</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>תוספות בניה לשם הרחבות יח"ד ברחוב המצור 5, ירושלים</t>
+          <t>הפיכת שטח שרות לעיקרי רח' עמק רפאים 13, ירושלים</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -29037,7 +29041,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G326" t="inlineStr"/>
@@ -29048,10 +29052,10 @@
       <c r="L326" t="inlineStr"/>
       <c r="M326" t="inlineStr"/>
       <c r="N326" t="n">
-        <v>0.793</v>
+        <v>1.194</v>
       </c>
       <c r="O326" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="P326" t="inlineStr">
         <is>
@@ -29060,11 +29064,11 @@
       </c>
       <c r="Q326" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005496000/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005380806/310</t>
         </is>
       </c>
       <c r="R326" t="n">
-        <v>1005496000</v>
+        <v>1005380806</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
@@ -29073,29 +29077,29 @@
       </c>
       <c r="T326" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>101-1549260</t>
+          <t>101-1523851</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>הסדנא 2 - תוספת שטחים</t>
+          <t>תוספות בניה לשם הרחבות יח"ד ברחוב המצור 5, ירושלים</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>במילוי תנאים להפקדה</t>
+          <t>בבדיקה תכנונית</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>החלטה בדיון</t>
+          <t>קיום תנאי סף</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -29105,29 +29109,21 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G327" t="inlineStr"/>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr"/>
       <c r="M327" t="inlineStr"/>
       <c r="N327" t="n">
-        <v>3.69</v>
+        <v>0.793</v>
       </c>
       <c r="O327" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="P327" t="inlineStr">
         <is>
@@ -29136,37 +29132,42 @@
       </c>
       <c r="Q327" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005512104/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005496000/310</t>
         </is>
       </c>
       <c r="R327" t="n">
-        <v>1005512104</v>
+        <v>1005496000</v>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
       </c>
       <c r="T327" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-02-05</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>101-1371368</t>
+          <t>101-1549260</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>פינוי בינוי ברחוב רשב"ג 4 - בן זכאי</t>
+          <t>הסדנא 2 - תוספת שטחים</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>בבדיקה תכנונית</t>
+          <t>במילוי תנאים להפקדה</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>קיום תנאי סף</t>
+          <t>החלטה בדיון</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -29176,25 +29177,29 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G328" t="inlineStr"/>
       <c r="H328" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="I328" t="inlineStr"/>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr"/>
       <c r="M328" t="inlineStr"/>
       <c r="N328" t="n">
-        <v>1.7</v>
+        <v>3.69</v>
       </c>
       <c r="O328" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="P328" t="inlineStr">
         <is>
@@ -29203,42 +29208,37 @@
       </c>
       <c r="Q328" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005403390/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005512104/310</t>
         </is>
       </c>
       <c r="R328" t="n">
-        <v>1005403390</v>
-      </c>
-      <c r="S328" t="inlineStr">
-        <is>
-          <t>ירושלים</t>
-        </is>
+        <v>1005512104</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>101-1575943</t>
+          <t>101-1371368</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>תוספת קומה ושטחי בניה ברחוב המערבים 8</t>
+          <t>פינוי בינוי ברחוב רשב"ג 4 - בן זכאי</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>הכרעה בהתנגדויות / אישור</t>
+          <t>בבדיקה תכנונית</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>בתהליך הפקדה</t>
+          <t>קיום תנאי סף</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -29248,41 +29248,25 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G329" t="inlineStr"/>
       <c r="H329" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr"/>
+      <c r="J329" t="inlineStr"/>
+      <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr"/>
-      <c r="M329" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
+      <c r="M329" t="inlineStr"/>
       <c r="N329" t="n">
-        <v>0.152</v>
+        <v>1.7</v>
       </c>
       <c r="O329" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="P329" t="inlineStr">
         <is>
@@ -29291,11 +29275,11 @@
       </c>
       <c r="Q329" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005527870/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005403390/310</t>
         </is>
       </c>
       <c r="R329" t="n">
-        <v>1005527870</v>
+        <v>1005403390</v>
       </c>
       <c r="S329" t="inlineStr">
         <is>
@@ -29304,29 +29288,29 @@
       </c>
       <c r="T329" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>101-1475011</t>
+          <t>101-1575943</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>רחוב האומן, תלפיות, ירושלים</t>
+          <t>תוספת קומה ושטחי בניה ברחוב המערבים 8</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>בבדיקה תכנונית</t>
+          <t>הכרעה בהתנגדויות / אישור</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>קיום תנאי סף</t>
+          <t>בתהליך הפקדה</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -29336,25 +29320,41 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G330" t="inlineStr"/>
       <c r="H330" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="I330" t="inlineStr"/>
-      <c r="J330" t="inlineStr"/>
-      <c r="K330" t="inlineStr"/>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr"/>
-      <c r="M330" t="inlineStr"/>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="N330" t="n">
-        <v>33614</v>
+        <v>0.152</v>
       </c>
       <c r="O330" t="n">
-        <v>33.5</v>
+        <v>0.2</v>
       </c>
       <c r="P330" t="inlineStr">
         <is>
@@ -29363,11 +29363,11 @@
       </c>
       <c r="Q330" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005465852/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005527870/310</t>
         </is>
       </c>
       <c r="R330" t="n">
-        <v>1005465852</v>
+        <v>1005527870</v>
       </c>
       <c r="S330" t="inlineStr">
         <is>
@@ -29376,19 +29376,19 @@
       </c>
       <c r="T330" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>101-1563642</t>
+          <t>101-1475011</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>התחדשות עירונית אריה בעהם ירושלים</t>
+          <t>רחוב האומן, תלפיות, ירושלים</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -29408,13 +29408,13 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G331" t="inlineStr"/>
       <c r="H331" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
@@ -29423,10 +29423,10 @@
       <c r="L331" t="inlineStr"/>
       <c r="M331" t="inlineStr"/>
       <c r="N331" t="n">
-        <v>5.224</v>
+        <v>33614</v>
       </c>
       <c r="O331" t="n">
-        <v>5.2</v>
+        <v>33.5</v>
       </c>
       <c r="P331" t="inlineStr">
         <is>
@@ -29435,11 +29435,11 @@
       </c>
       <c r="Q331" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005520878/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005465852/310</t>
         </is>
       </c>
       <c r="R331" t="n">
-        <v>1005520878</v>
+        <v>1005465852</v>
       </c>
       <c r="S331" t="inlineStr">
         <is>
@@ -29448,19 +29448,19 @@
       </c>
       <c r="T331" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>101-1554773</t>
+          <t>101-1563642</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>הריסת מבנה ישן ובניית מבנה מגורים+ מסחר חדש ברחוב יוסי בן יועזר 21</t>
+          <t>התחדשות עירונית אריה בעהם ירושלים</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -29480,13 +29480,13 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G332" t="inlineStr"/>
       <c r="H332" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
@@ -29495,10 +29495,10 @@
       <c r="L332" t="inlineStr"/>
       <c r="M332" t="inlineStr"/>
       <c r="N332" t="n">
-        <v>0.716</v>
+        <v>5.224</v>
       </c>
       <c r="O332" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="P332" t="inlineStr">
         <is>
@@ -29507,11 +29507,11 @@
       </c>
       <c r="Q332" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005515600/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005520878/310</t>
         </is>
       </c>
       <c r="R332" t="n">
-        <v>1005515600</v>
+        <v>1005520878</v>
       </c>
       <c r="S332" t="inlineStr">
         <is>
@@ -29520,19 +29520,19 @@
       </c>
       <c r="T332" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>101-1587294</t>
+          <t>101-1554773</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>התחדשות עירונית - פארק תלפיות</t>
+          <t>הריסת מבנה ישן ובניית מבנה מגורים+ מסחר חדש ברחוב יוסי בן יועזר 21</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -29552,13 +29552,13 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G333" t="inlineStr"/>
       <c r="H333" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
@@ -29567,10 +29567,10 @@
       <c r="L333" t="inlineStr"/>
       <c r="M333" t="inlineStr"/>
       <c r="N333" t="n">
-        <v>27.35</v>
+        <v>0.716</v>
       </c>
       <c r="O333" t="n">
-        <v>27.3</v>
+        <v>0.7</v>
       </c>
       <c r="P333" t="inlineStr">
         <is>
@@ -29579,11 +29579,11 @@
       </c>
       <c r="Q333" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005534766/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005515600/310</t>
         </is>
       </c>
       <c r="R333" t="n">
-        <v>1005534766</v>
+        <v>1005515600</v>
       </c>
       <c r="S333" t="inlineStr">
         <is>
@@ -29592,19 +29592,19 @@
       </c>
       <c r="T333" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>101-1550508</t>
+          <t>101-1587294</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>תוספות בינוי לבנין מגורים ברחוב הטייסים 31, ירושלים</t>
+          <t>התחדשות עירונית - פארק תלפיות</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -29614,7 +29614,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>הועברה לו. מקומית</t>
+          <t>קיום תנאי סף</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -29624,13 +29624,13 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G334" t="inlineStr"/>
       <c r="H334" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I334" t="inlineStr"/>
@@ -29639,10 +29639,10 @@
       <c r="L334" t="inlineStr"/>
       <c r="M334" t="inlineStr"/>
       <c r="N334" t="n">
-        <v>1.423</v>
+        <v>27.35</v>
       </c>
       <c r="O334" t="n">
-        <v>1.4</v>
+        <v>27.3</v>
       </c>
       <c r="P334" t="inlineStr">
         <is>
@@ -29651,11 +29651,11 @@
       </c>
       <c r="Q334" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005512768/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005534766/310</t>
         </is>
       </c>
       <c r="R334" t="n">
-        <v>1005512768</v>
+        <v>1005534766</v>
       </c>
       <c r="S334" t="inlineStr">
         <is>
@@ -29664,19 +29664,19 @@
       </c>
       <c r="T334" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>101-1496504</t>
+          <t>101-1550508</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>בן מימון 37 תוספת שטחים</t>
+          <t>תוספות בינוי לבנין מגורים ברחוב הטייסים 31, ירושלים</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -29686,7 +29686,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>קיום תנאי סף</t>
+          <t>הועברה לו. מקומית</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -29696,21 +29696,25 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G335" t="inlineStr"/>
-      <c r="H335" t="inlineStr"/>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
       <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr"/>
       <c r="M335" t="inlineStr"/>
       <c r="N335" t="n">
-        <v>0.726</v>
+        <v>1.423</v>
       </c>
       <c r="O335" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="P335" t="inlineStr">
         <is>
@@ -29719,11 +29723,11 @@
       </c>
       <c r="Q335" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005479156/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005512768/310</t>
         </is>
       </c>
       <c r="R335" t="n">
-        <v>1005479156</v>
+        <v>1005512768</v>
       </c>
       <c r="S335" t="inlineStr">
         <is>
@@ -29732,19 +29736,19 @@
       </c>
       <c r="T335" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>101-1460088</t>
+          <t>101-1496504</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>הריסה והקמת מבנה מגורים חדש בשמעוני 36</t>
+          <t>בן מימון 37 תוספת שטחים</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -29764,25 +29768,21 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G336" t="inlineStr"/>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
+      <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr"/>
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr"/>
       <c r="L336" t="inlineStr"/>
       <c r="M336" t="inlineStr"/>
       <c r="N336" t="n">
-        <v>0.771</v>
+        <v>0.726</v>
       </c>
       <c r="O336" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="P336" t="inlineStr">
         <is>
@@ -29791,11 +29791,11 @@
       </c>
       <c r="Q336" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005456952/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005479156/310</t>
         </is>
       </c>
       <c r="R336" t="n">
-        <v>1005456952</v>
+        <v>1005479156</v>
       </c>
       <c r="S336" t="inlineStr">
         <is>
@@ -29804,29 +29804,29 @@
       </c>
       <c r="T336" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>101-1487560</t>
+          <t>101-1460088</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>שינוי קווי בניין לשם שינוי תכנון ללא תוספת שטחים-מבוא יורם 1</t>
+          <t>הריסה והקמת מבנה מגורים חדש בשמעוני 36</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>הפקדה להתנגדויות/השגות</t>
+          <t>בבדיקה תכנונית</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>פרסום הפקדה</t>
+          <t>קיום תנאי סף</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -29836,21 +29836,25 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G337" t="inlineStr"/>
-      <c r="H337" t="inlineStr"/>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="I337" t="inlineStr"/>
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr"/>
       <c r="M337" t="inlineStr"/>
       <c r="N337" t="n">
-        <v>0.607</v>
+        <v>0.771</v>
       </c>
       <c r="O337" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="P337" t="inlineStr">
         <is>
@@ -29859,11 +29863,11 @@
       </c>
       <c r="Q337" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005473546/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005456952/310</t>
         </is>
       </c>
       <c r="R337" t="n">
-        <v>1005473546</v>
+        <v>1005456952</v>
       </c>
       <c r="S337" t="inlineStr">
         <is>
@@ -29872,29 +29876,29 @@
       </c>
       <c r="T337" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>101-1590793</t>
+          <t>101-1487560</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>דרום מערב מלחה - מרכז ספורט, תעסוקה ומגורים</t>
+          <t>שינוי קווי בניין לשם שינוי תכנון ללא תוספת שטחים-מבוא יורם 1</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>בבדיקה תכנונית</t>
+          <t>הפקדה להתנגדויות/השגות</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>קיום תנאי סף</t>
+          <t>פרסום הפקדה</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -29904,54 +29908,55 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G338" t="inlineStr"/>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
+      <c r="H338" t="inlineStr"/>
       <c r="I338" t="inlineStr"/>
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr"/>
       <c r="M338" t="inlineStr"/>
       <c r="N338" t="n">
-        <v>199.29</v>
+        <v>0.607</v>
       </c>
       <c r="O338" t="n">
-        <v>44.9</v>
+        <v>0.6</v>
       </c>
       <c r="P338" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005536476/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005473546/310</t>
         </is>
       </c>
       <c r="R338" t="n">
-        <v>1005536476</v>
+        <v>1005473546</v>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
       </c>
       <c r="T338" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>101-1551324</t>
+          <t>101-1590439</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>עדכון לתכנית 1449א</t>
+          <t>הפורצים 17-19, פינוי בינוי</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -29961,31 +29966,35 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>קיום תנאי סף</t>
+          <t>קבלת תכנית</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>תכנית מפורטת</t>
+          <t>תכנית מתאר מקומית</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G339" t="inlineStr"/>
-      <c r="H339" t="inlineStr"/>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
       <c r="I339" t="inlineStr"/>
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr"/>
       <c r="M339" t="inlineStr"/>
       <c r="N339" t="n">
-        <v>0.41</v>
+        <v>3.231</v>
       </c>
       <c r="O339" t="n">
-        <v>0.1</v>
+        <v>3.2</v>
       </c>
       <c r="P339" t="inlineStr">
         <is>
@@ -29994,11 +30003,11 @@
       </c>
       <c r="Q339" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005513260/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005536258/310</t>
         </is>
       </c>
       <c r="R339" t="n">
-        <v>1005513260</v>
+        <v>1005536258</v>
       </c>
       <c r="S339" t="inlineStr">
         <is>
@@ -30007,19 +30016,19 @@
       </c>
       <c r="T339" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>101-1439413</t>
+          <t>101-1590793</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>הטייסים 33</t>
+          <t>דרום מערב מלחה - מרכז ספורט, תעסוקה ומגורים</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -30039,55 +30048,54 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G340" t="inlineStr"/>
-      <c r="H340" t="inlineStr"/>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
       <c r="I340" t="inlineStr"/>
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr"/>
       <c r="L340" t="inlineStr"/>
       <c r="M340" t="inlineStr"/>
       <c r="N340" t="n">
-        <v>0.93</v>
+        <v>199.29</v>
       </c>
       <c r="O340" t="n">
-        <v>0.9</v>
+        <v>44.9</v>
       </c>
       <c r="P340" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005444316/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005536476/310</t>
         </is>
       </c>
       <c r="R340" t="n">
-        <v>1005444316</v>
-      </c>
-      <c r="S340" t="inlineStr">
-        <is>
-          <t>ירושלים</t>
-        </is>
+        <v>1005536476</v>
       </c>
       <c r="T340" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>101-1614130</t>
+          <t>101-1551324</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>הקמת בניין מגורים חדש ברחוב קנאי הגליל 18 בירושלים</t>
+          <t>עדכון לתכנית 1449א</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -30102,30 +30110,26 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>תכנית מתאר מקומית</t>
+          <t>תכנית מפורטת</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G341" t="inlineStr"/>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
+      <c r="H341" t="inlineStr"/>
       <c r="I341" t="inlineStr"/>
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr"/>
       <c r="L341" t="inlineStr"/>
       <c r="M341" t="inlineStr"/>
       <c r="N341" t="n">
-        <v>0.596</v>
+        <v>0.41</v>
       </c>
       <c r="O341" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="P341" t="inlineStr">
         <is>
@@ -30134,11 +30138,11 @@
       </c>
       <c r="Q341" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005550842/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005513260/310</t>
         </is>
       </c>
       <c r="R341" t="n">
-        <v>1005550842</v>
+        <v>1005513260</v>
       </c>
       <c r="S341" t="inlineStr">
         <is>
@@ -30147,19 +30151,19 @@
       </c>
       <c r="T341" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>101-1543669</t>
+          <t>101-1439413</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>הרחבות יח"ד קיימות ותוספת יח"ד חדשה ברח' חננאל 17 ירושלים</t>
+          <t>הטייסים 33</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -30179,7 +30183,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G342" t="inlineStr"/>
@@ -30190,10 +30194,10 @@
       <c r="L342" t="inlineStr"/>
       <c r="M342" t="inlineStr"/>
       <c r="N342" t="n">
-        <v>0.666</v>
+        <v>0.93</v>
       </c>
       <c r="O342" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="P342" t="inlineStr">
         <is>
@@ -30202,11 +30206,11 @@
       </c>
       <c r="Q342" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005508986/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005444316/310</t>
         </is>
       </c>
       <c r="R342" t="n">
-        <v>1005508986</v>
+        <v>1005444316</v>
       </c>
       <c r="S342" t="inlineStr">
         <is>
@@ -30215,19 +30219,19 @@
       </c>
       <c r="T342" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>101-1551530</t>
+          <t>101-1614130</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>הרחבת יח"ד קיימות ברח' טשרניחובסקי 72, ירושלים</t>
+          <t>הקמת בניין מגורים חדש ברחוב קנאי הגליל 18 בירושלים</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -30247,21 +30251,25 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G343" t="inlineStr"/>
-      <c r="H343" t="inlineStr"/>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="I343" t="inlineStr"/>
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr"/>
       <c r="M343" t="inlineStr"/>
       <c r="N343" t="n">
-        <v>1</v>
+        <v>0.596</v>
       </c>
       <c r="O343" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="P343" t="inlineStr">
         <is>
@@ -30270,11 +30278,11 @@
       </c>
       <c r="Q343" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005513454/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005550842/310</t>
         </is>
       </c>
       <c r="R343" t="n">
-        <v>1005513454</v>
+        <v>1005550842</v>
       </c>
       <c r="S343" t="inlineStr">
         <is>
@@ -30283,19 +30291,19 @@
       </c>
       <c r="T343" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>101-1571991</t>
+          <t>101-1543669</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>תוספת שטחים, קומות חניה ויח"ד ברח' אלכסנדריון 17, ירושלים</t>
+          <t>הרחבות יח"ד קיימות ותוספת יח"ד חדשה ברח' חננאל 17 ירושלים</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -30326,10 +30334,10 @@
       <c r="L344" t="inlineStr"/>
       <c r="M344" t="inlineStr"/>
       <c r="N344" t="n">
-        <v>0.784</v>
+        <v>0.666</v>
       </c>
       <c r="O344" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="P344" t="inlineStr">
         <is>
@@ -30338,11 +30346,11 @@
       </c>
       <c r="Q344" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005525550/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005508986/310</t>
         </is>
       </c>
       <c r="R344" t="n">
-        <v>1005525550</v>
+        <v>1005508986</v>
       </c>
       <c r="S344" t="inlineStr">
         <is>
@@ -30358,12 +30366,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>101-1533025</t>
+          <t>101-1551530</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>תוספת קומה לשם הרחבת יח"ד קיימות, רחוב הטייסים 48</t>
+          <t>הרחבת יח"ד קיימות ברח' טשרניחובסקי 72, ירושלים</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -30383,7 +30391,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G345" t="inlineStr"/>
@@ -30394,10 +30402,10 @@
       <c r="L345" t="inlineStr"/>
       <c r="M345" t="inlineStr"/>
       <c r="N345" t="n">
-        <v>0.475</v>
+        <v>1</v>
       </c>
       <c r="O345" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P345" t="inlineStr">
         <is>
@@ -30406,11 +30414,11 @@
       </c>
       <c r="Q345" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005502314/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005513454/310</t>
         </is>
       </c>
       <c r="R345" t="n">
-        <v>1005502314</v>
+        <v>1005513454</v>
       </c>
       <c r="S345" t="inlineStr">
         <is>
@@ -30419,19 +30427,19 @@
       </c>
       <c r="T345" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>101-1608678</t>
+          <t>101-1571991</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>תוספת שטחים לייעוד מסחר ותעסוקה ברח' ניקנור 38</t>
+          <t>תוספת שטחים, קומות חניה ויח"ד ברח' אלכסנדריון 17, ירושלים</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -30451,25 +30459,21 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G346" t="inlineStr"/>
-      <c r="H346" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
+      <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr"/>
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr"/>
       <c r="L346" t="inlineStr"/>
       <c r="M346" t="inlineStr"/>
       <c r="N346" t="n">
-        <v>0.7</v>
+        <v>0.784</v>
       </c>
       <c r="O346" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="P346" t="inlineStr">
         <is>
@@ -30478,11 +30482,11 @@
       </c>
       <c r="Q346" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005547722/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005525550/310</t>
         </is>
       </c>
       <c r="R346" t="n">
-        <v>1005547722</v>
+        <v>1005525550</v>
       </c>
       <c r="S346" t="inlineStr">
         <is>
@@ -30491,19 +30495,19 @@
       </c>
       <c r="T346" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>101-1547348</t>
+          <t>101-1533025</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>רכבת קלה ירושלים - קו סגול</t>
+          <t>תוספת קומה לשם הרחבת יח"ד קיימות, רחוב הטייסים 48</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -30523,54 +30527,55 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G347" t="inlineStr"/>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
+      <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr"/>
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr"/>
       <c r="L347" t="inlineStr"/>
       <c r="M347" t="inlineStr"/>
       <c r="N347" t="n">
-        <v>235.47</v>
+        <v>0.475</v>
       </c>
       <c r="O347" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="P347" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="Q347" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005510812/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005502314/310</t>
         </is>
       </c>
       <c r="R347" t="n">
-        <v>1005510812</v>
+        <v>1005502314</v>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
       </c>
       <c r="T347" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>101-1566306</t>
+          <t>101-1608678</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>רחוב חלפתא 3 בירושלים הרחבת דיור לדירה קיימת</t>
+          <t>תוספת שטחים לייעוד מסחר ותעסוקה ברח' ניקנור 38</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -30578,6 +30583,11 @@
           <t>בבדיקה תכנונית</t>
         </is>
       </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>קיום תנאי סף</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>תכנית מתאר מקומית</t>
@@ -30585,21 +30595,25 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G348" t="inlineStr"/>
-      <c r="H348" t="inlineStr"/>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="I348" t="inlineStr"/>
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr"/>
       <c r="L348" t="inlineStr"/>
       <c r="M348" t="inlineStr"/>
       <c r="N348" t="n">
-        <v>1607</v>
+        <v>0.7</v>
       </c>
       <c r="O348" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="P348" t="inlineStr">
         <is>
@@ -30608,11 +30622,11 @@
       </c>
       <c r="Q348" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005522198/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005547722/310</t>
         </is>
       </c>
       <c r="R348" t="n">
-        <v>1005522198</v>
+        <v>1005547722</v>
       </c>
       <c r="S348" t="inlineStr">
         <is>
@@ -30621,29 +30635,29 @@
       </c>
       <c r="T348" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>101-0110510</t>
+          <t>101-1547348</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>מתחם פינוי ובינוי אלכסנדריון, גוננים - ירושלים</t>
+          <t>רכבת קלה ירושלים - קו סגול</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>אישור</t>
+          <t>בבדיקה תכנונית</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>התכנית אושרה</t>
+          <t>קיום תנאי סף</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -30651,107 +30665,90 @@
           <t>תכנית מתאר מקומית</t>
         </is>
       </c>
-      <c r="F349" t="inlineStr"/>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>2014-10-23</t>
-        </is>
-      </c>
-      <c r="H349" t="inlineStr"/>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr"/>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="I349" t="inlineStr"/>
-      <c r="J349" t="inlineStr">
-        <is>
-          <t>2014-08-12</t>
-        </is>
-      </c>
+      <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr"/>
-      <c r="L349" t="inlineStr">
-        <is>
-          <t>2015-06-28</t>
-        </is>
-      </c>
-      <c r="M349" t="inlineStr">
-        <is>
-          <t>2014-10-11</t>
-        </is>
-      </c>
+      <c r="L349" t="inlineStr"/>
+      <c r="M349" t="inlineStr"/>
       <c r="N349" t="n">
-        <v>18.687</v>
+        <v>235.47</v>
       </c>
       <c r="O349" t="n">
-        <v>19.4</v>
+        <v>5.8</v>
       </c>
       <c r="P349" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="Q349" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1000248067/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005510812/310</t>
         </is>
       </c>
       <c r="R349" t="n">
-        <v>1000248067</v>
-      </c>
-      <c r="S349" t="inlineStr">
-        <is>
-          <t>ירושלים</t>
-        </is>
+        <v>1005510812</v>
       </c>
       <c r="T349" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>101-1158146</t>
+          <t>101-1566306</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>בית הנוער העברי</t>
+          <t>רחוב חלפתא 3 בירושלים הרחבת דיור לדירה קיימת</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>במילוי תנאים להפקדה</t>
+          <t>בבדיקה תכנונית</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>החלטה בדיון</t>
+          <t>קיום תנאי סף</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>תכנית מפורטת</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr"/>
+          <t>תכנית מתאר מקומית</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
       <c r="G350" t="inlineStr"/>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr"/>
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr"/>
       <c r="M350" t="inlineStr"/>
       <c r="N350" t="n">
-        <v>26.859</v>
+        <v>1607</v>
       </c>
       <c r="O350" t="n">
-        <v>26.9</v>
+        <v>1.6</v>
       </c>
       <c r="P350" t="inlineStr">
         <is>
@@ -30760,11 +30757,11 @@
       </c>
       <c r="Q350" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005267674/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005522198/310</t>
         </is>
       </c>
       <c r="R350" t="n">
-        <v>1005267674</v>
+        <v>1005522198</v>
       </c>
       <c r="S350" t="inlineStr">
         <is>
@@ -30773,29 +30770,29 @@
       </c>
       <c r="T350" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>101-1236579</t>
+          <t>101-0110510</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>מתחם גוננים</t>
+          <t>מתחם פינוי ובינוי אלכסנדריון, גוננים - ירושלים</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>במילוי תנאים להפקדה</t>
+          <t>אישור</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>החלטה בדיון</t>
+          <t>התכנית אושרה</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -30804,26 +30801,34 @@
         </is>
       </c>
       <c r="F351" t="inlineStr"/>
-      <c r="G351" t="inlineStr"/>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="J351" t="inlineStr"/>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>2014-10-23</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr"/>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>2014-08-12</t>
+        </is>
+      </c>
       <c r="K351" t="inlineStr"/>
-      <c r="L351" t="inlineStr"/>
-      <c r="M351" t="inlineStr"/>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>2015-06-28</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>2014-10-11</t>
+        </is>
+      </c>
       <c r="N351" t="n">
-        <v>58.047</v>
+        <v>18.687</v>
       </c>
       <c r="O351" t="n">
-        <v>58.1</v>
+        <v>19.4</v>
       </c>
       <c r="P351" t="inlineStr">
         <is>
@@ -30832,11 +30837,11 @@
       </c>
       <c r="Q351" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/1005317984/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1000248067/310</t>
         </is>
       </c>
       <c r="R351" t="n">
-        <v>1005317984</v>
+        <v>1000248067</v>
       </c>
       <c r="S351" t="inlineStr">
         <is>
@@ -30845,127 +30850,271 @@
       </c>
       <c r="T351" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2025-07-27</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>תתל/ 108/ 77-78</t>
+          <t>101-1158146</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>מסילת רכבת בירושלים</t>
+          <t>בית הנוער העברי</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>אישור</t>
+          <t>במילוי תנאים להפקדה</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>התכנית אושרה</t>
+          <t>החלטה בדיון</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>הודעה לפי סעיף 77 ו 78 לחוק התכנון והבניה</t>
+          <t>תכנית מפורטת</t>
         </is>
       </c>
       <c r="F352" t="inlineStr"/>
       <c r="G352" t="inlineStr"/>
-      <c r="H352" t="inlineStr"/>
-      <c r="I352" t="inlineStr"/>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr"/>
       <c r="L352" t="inlineStr"/>
       <c r="M352" t="inlineStr"/>
       <c r="N352" t="n">
-        <v>1000.664</v>
+        <v>26.859</v>
       </c>
       <c r="O352" t="n">
-        <v>83.09999999999999</v>
+        <v>26.9</v>
       </c>
       <c r="P352" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="Q352" t="inlineStr">
         <is>
-          <t>https://mavat.iplan.gov.il/SV4/1/99001010241/310</t>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005267674/310</t>
         </is>
       </c>
       <c r="R352" t="n">
-        <v>99001010241</v>
+        <v>1005267674</v>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
       </c>
       <c r="T352" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>תתל/ 108/ סעיף-78-77</t>
+          <t>101-1236579</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>מסילת רכבת בירושלים</t>
+          <t>מתחם גוננים</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>אישור</t>
+          <t>במילוי תנאים להפקדה</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>התכנית אושרה</t>
+          <t>החלטה בדיון</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>הודעה לפי ס' 76 ג1 ו-77 וקביעת תנאים לפי ס' 78</t>
+          <t>תכנית מתאר מקומית</t>
         </is>
       </c>
       <c r="F353" t="inlineStr"/>
       <c r="G353" t="inlineStr"/>
-      <c r="H353" t="inlineStr"/>
-      <c r="I353" t="inlineStr"/>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr"/>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
+      <c r="L353" t="inlineStr"/>
       <c r="M353" t="inlineStr"/>
       <c r="N353" t="n">
+        <v>58.047</v>
+      </c>
+      <c r="O353" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>https://mavat.iplan.gov.il/SV4/1/1005317984/310</t>
+        </is>
+      </c>
+      <c r="R353" t="n">
+        <v>1005317984</v>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>תתל/ 108/ 77-78</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>מסילת רכבת בירושלים</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>אישור</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>התכנית אושרה</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>הודעה לפי סעיף 77 ו 78 לחוק התכנון והבניה</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr"/>
+      <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr"/>
+      <c r="J354" t="inlineStr"/>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr"/>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="n">
+        <v>1000.664</v>
+      </c>
+      <c r="O354" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>https://mavat.iplan.gov.il/SV4/1/99001010241/310</t>
+        </is>
+      </c>
+      <c r="R354" t="n">
+        <v>99001010241</v>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>תתל/ 108/ סעיף-78-77</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>מסילת רכבת בירושלים</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>אישור</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>התכנית אושרה</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>הודעה לפי ס' 76 ג1 ו-77 וקביעת תנאים לפי ס' 78</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr"/>
+      <c r="H355" t="inlineStr"/>
+      <c r="I355" t="inlineStr"/>
+      <c r="J355" t="inlineStr"/>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="n">
         <v>777.669</v>
       </c>
-      <c r="O353" t="n">
+      <c r="O355" t="n">
         <v>80.3</v>
       </c>
-      <c r="P353" t="inlineStr">
+      <c r="P355" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
       </c>
-      <c r="Q353" t="inlineStr">
+      <c r="Q355" t="inlineStr">
         <is>
           <t>https://mavat.iplan.gov.il/SV4/1/99005229984/310</t>
         </is>
       </c>
-      <c r="R353" t="n">
+      <c r="R355" t="n">
         <v>99005229984</v>
       </c>
-      <c r="T353" t="inlineStr">
+      <c r="T355" t="inlineStr">
         <is>
           <t>2022-10-26</t>
         </is>
@@ -31014,7 +31163,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -31030,7 +31179,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>הפקדה להתנגדויות/השגות</t>
+          <t>הכרעה בהתנגדויות / אישור</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -31040,7 +31189,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>הכרעה בהתנגדויות / אישור</t>
+          <t>הפקדה להתנגדויות/השגות</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -31076,7 +31225,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="11">
